--- a/docs/Danh sách nhân viên HD RL.xlsx
+++ b/docs/Danh sách nhân viên HD RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hansungbolt-overtime\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6941724-6A9E-440C-AD81-2D896DF5FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577F437D-DA6C-4EF7-B96B-7A08DD79AA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-50" yWindow="-50" windowWidth="38500" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>VÕ VĂN TRÌNH</t>
   </si>
   <si>
-    <t>NGUYỄN VĂN TÙNG (A)</t>
-  </si>
-  <si>
     <t>HÀ QUỐC ĐIỆP</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>RL</t>
+  </si>
+  <si>
+    <t>NGUYỄN VĂN TÙNG</t>
   </si>
 </sst>
 </file>
@@ -138,34 +138,34 @@
   <numFmts count="30">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="\(yy/mm/dd\)"/>
-    <numFmt numFmtId="167" formatCode="&quot;(&quot;0%&quot;)   &quot;;[Red]\-&quot;(&quot;0%&quot;)   &quot;;&quot;?    &quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;(&quot;0.00%&quot;)   &quot;;[Red]\-&quot;(&quot;0.00%&quot;)   &quot;;&quot;?    &quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00%;[Red]\-0.00%;&quot;?&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,###,###,###,##0"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="\$#,##0\ ;\(\$#,##0\)"/>
-    <numFmt numFmtId="175" formatCode="#,##0\ _A_T_S;[Red]\-#,##0\ _A_T_S"/>
-    <numFmt numFmtId="176" formatCode="#,##0.00\ _A_T_S;[Red]\-#,##0.00\ _A_T_S"/>
-    <numFmt numFmtId="177" formatCode="&quot;False&quot;;;&quot;True&quot;;&quot;Character&quot;"/>
-    <numFmt numFmtId="178" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="0.0000;\-0.0000;0;&quot;Character&quot;"/>
-    <numFmt numFmtId="180" formatCode="#,##0.00;\-#,##0.00;0;&quot;Character&quot;"/>
-    <numFmt numFmtId="181" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="182" formatCode="&quot;False&quot;;&quot;False&quot;;&quot;True&quot;;@"/>
-    <numFmt numFmtId="183" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
-    <numFmt numFmtId="184" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
-    <numFmt numFmtId="185" formatCode="&quot;(&quot;0%&quot;)   &quot;;[Red]\-&quot;(&quot;0%&quot;)   &quot;;&quot;－    &quot;"/>
-    <numFmt numFmtId="186" formatCode="&quot;(&quot;0.00%&quot;)   &quot;;[Red]\-&quot;(&quot;0.00%&quot;)   &quot;;&quot;－    &quot;"/>
-    <numFmt numFmtId="187" formatCode="0.00%;[Red]\-0.00%;&quot;－&quot;"/>
-    <numFmt numFmtId="188" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="189" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="191" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="192" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="\(yy/mm/dd\)"/>
+    <numFmt numFmtId="166" formatCode="&quot;(&quot;0%&quot;)   &quot;;[Red]\-&quot;(&quot;0%&quot;)   &quot;;&quot;?    &quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;(&quot;0.00%&quot;)   &quot;;[Red]\-&quot;(&quot;0.00%&quot;)   &quot;;&quot;?    &quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00%;[Red]\-0.00%;&quot;?&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,###,###,###,##0"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0\ ;\(\$#,##0\)"/>
+    <numFmt numFmtId="174" formatCode="#,##0\ _A_T_S;[Red]\-#,##0\ _A_T_S"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00\ _A_T_S;[Red]\-#,##0.00\ _A_T_S"/>
+    <numFmt numFmtId="176" formatCode="&quot;False&quot;;;&quot;True&quot;;&quot;Character&quot;"/>
+    <numFmt numFmtId="177" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="0.0000;\-0.0000;0;&quot;Character&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00;\-#,##0.00;0;&quot;Character&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="181" formatCode="&quot;False&quot;;&quot;False&quot;;&quot;True&quot;;@"/>
+    <numFmt numFmtId="182" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
+    <numFmt numFmtId="183" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="184" formatCode="&quot;(&quot;0%&quot;)   &quot;;[Red]\-&quot;(&quot;0%&quot;)   &quot;;&quot;－    &quot;"/>
+    <numFmt numFmtId="185" formatCode="&quot;(&quot;0.00%&quot;)   &quot;;[Red]\-&quot;(&quot;0.00%&quot;)   &quot;;&quot;－    &quot;"/>
+    <numFmt numFmtId="186" formatCode="0.00%;[Red]\-0.00%;&quot;－&quot;"/>
+    <numFmt numFmtId="187" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="188" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;&quot;¥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="191" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
   <fonts count="106">
     <font>
@@ -1426,20 +1426,20 @@
   <cellStyleXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" applyBorder="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" applyBorder="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1541,10 +1541,10 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="20" fillId="17" borderId="3" applyBorder="0">
+    <xf numFmtId="169" fontId="20" fillId="17" borderId="3" applyBorder="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="17" borderId="4" applyBorder="0"/>
+    <xf numFmtId="170" fontId="21" fillId="17" borderId="4" applyBorder="0"/>
     <xf numFmtId="2" fontId="21" fillId="17" borderId="4" applyBorder="0"/>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1567,9 +1567,9 @@
     <xf numFmtId="40" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0">
       <alignment horizontal="centerContinuous"/>
@@ -1577,19 +1577,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" applyBorder="0">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="174" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="175" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1604,8 +1604,8 @@
     <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="35" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1646,15 +1646,15 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="42" fillId="2" borderId="16" applyBorder="0">
+    <xf numFmtId="178" fontId="42" fillId="2" borderId="16" applyBorder="0">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="41" fillId="2" borderId="13" applyBorder="0">
+    <xf numFmtId="179" fontId="41" fillId="2" borderId="13" applyBorder="0">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="43" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1860,9 +1860,9 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="71" fillId="0" borderId="23"/>
+    <xf numFmtId="181" fontId="71" fillId="0" borderId="23"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="183" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1890,11 +1890,11 @@
     <xf numFmtId="0" fontId="74" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="184" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="187" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="75" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -1911,10 +1911,10 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="188" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="190" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="191" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="83" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -1964,7 +1964,7 @@
     </xf>
     <xf numFmtId="43" fontId="98" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1981,7 +1981,7 @@
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="192" fontId="102" fillId="0" borderId="0" xfId="277" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="102" fillId="0" borderId="0" xfId="277" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1995,9 +1995,6 @@
     </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="278">
@@ -2612,174 +2609,174 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="46">
       <c r="A1" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:3" s="5" customFormat="1">
       <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>13</v>
+      <c r="B8" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>14</v>
+      <c r="B10" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>16</v>
+      <c r="B11" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>21</v>
+      <c r="B12" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>20</v>
+      <c r="B13" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>17</v>
+      <c r="B14" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>22</v>
+      <c r="B15" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>24</v>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="5" customFormat="1">
@@ -2791,110 +2788,110 @@
       <c r="A18" s="7">
         <v>1</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A19" s="7">
         <v>2</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A20" s="7">
         <v>3</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>12</v>
+      <c r="B20" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A21" s="7">
         <v>4</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A22" s="7">
         <v>5</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A23" s="7">
         <v>6</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A24" s="7">
         <v>7</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A25" s="7">
         <v>8</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>15</v>
+      <c r="B25" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A26" s="7">
         <v>9</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>18</v>
+      <c r="B26" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="8" customFormat="1" ht="15.5">
       <c r="A27" s="7">
         <v>10</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>19</v>
+      <c r="B27" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="8" customFormat="1" ht="15.5">
@@ -2902,10 +2899,10 @@
         <v>11</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="6" customFormat="1">
